--- a/Contenu_MAJ_NOS_EvolANS/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/Contenu_MAJ_NOS_EvolANS/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-17T10:48:02+00:00</t>
+    <t>2024-06-18T13:19:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Contenu_MAJ_NOS_EvolANS/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/Contenu_MAJ_NOS_EvolANS/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T13:19:34+00:00</t>
+    <t>2024-06-18T13:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
